--- a/new-info53/web.xlsx
+++ b/new-info53/web.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\object\projectInfo\new-info53\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="21975" windowHeight="13665"/>
+    <workbookView windowWidth="14100" windowHeight="11145"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="14" r:id="rId1"/>
@@ -30,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
   <si>
     <t>domain</t>
   </si>
@@ -41,49 +46,49 @@
     <t>color2</t>
   </si>
   <si>
-    <t>hazysea.com</t>
+    <t>read.mellifluo.cloud</t>
+  </si>
+  <si>
+    <t>#41bbcb</t>
+  </si>
+  <si>
+    <t>sec.mellifluo.cloud</t>
+  </si>
+  <si>
+    <t>#6090b8</t>
+  </si>
+  <si>
+    <t>read.apodyopsis.site</t>
+  </si>
+  <si>
+    <t>#4d613c</t>
+  </si>
+  <si>
+    <t>sec.apodyopsis.site</t>
+  </si>
+  <si>
+    <t>#a9b4c4</t>
+  </si>
+  <si>
+    <t>color1</t>
+  </si>
+  <si>
+    <t>info</t>
+  </si>
+  <si>
+    <t>json</t>
+  </si>
+  <si>
+    <t>reticence.cloud</t>
   </si>
   <si>
     <t>#664b3a</t>
   </si>
   <si>
-    <t>baisemain.site</t>
+    <t>whirpool.fun</t>
   </si>
   <si>
     <t>#e07563</t>
-  </si>
-  <si>
-    <t>noctiluca.cloud</t>
-  </si>
-  <si>
-    <t>#41bbcb</t>
-  </si>
-  <si>
-    <t>xenolith.fun</t>
-  </si>
-  <si>
-    <t>#6090b8</t>
-  </si>
-  <si>
-    <t>zinniaea.fun</t>
-  </si>
-  <si>
-    <t>#4d613c</t>
-  </si>
-  <si>
-    <t>color1</t>
-  </si>
-  <si>
-    <t>info</t>
-  </si>
-  <si>
-    <t>json</t>
-  </si>
-  <si>
-    <t>reticence.cloud</t>
-  </si>
-  <si>
-    <t>whirpool.fun</t>
   </si>
   <si>
     <t>happwave.com</t>
@@ -369,7 +374,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="44">
+  <fills count="45">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -439,6 +444,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4D613C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9B4C4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -759,7 +770,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -783,16 +794,16 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -801,89 +812,89 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -922,38 +933,35 @@
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1367,196 +1375,192 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="14"/>
+      <c r="C2" s="10"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="14"/>
+      <c r="C3" s="10"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="21"/>
-      <c r="D4" s="22"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="21"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="21"/>
-      <c r="D5" s="22"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="21"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="21"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
+      <c r="A6" s="23"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="26"/>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
+      <c r="A8" s="25"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="25"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
+      <c r="A9" s="24"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="25"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
+      <c r="A10" s="24"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="25"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
+      <c r="A11" s="24"/>
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="25"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="25"/>
+      <c r="A12" s="24"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="24"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="25"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="25"/>
+      <c r="A13" s="24"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="24"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="25"/>
-      <c r="B14" s="25"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
+      <c r="A14" s="24"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="25"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
+      <c r="A15" s="24"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="25"/>
-      <c r="B16" s="25"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="25"/>
+      <c r="A16" s="24"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="25"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="25"/>
+      <c r="A17" s="24"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="25"/>
-      <c r="B18" s="25"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="25"/>
+      <c r="A18" s="24"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="25"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="25"/>
+      <c r="A19" s="24"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="24"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="25"/>
-      <c r="B20" s="25"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="25"/>
+      <c r="A20" s="24"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1582,24 +1586,24 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3">
@@ -1612,10 +1616,10 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>17</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>6</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3">
@@ -1631,9 +1635,9 @@
         <v>18</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="14"/>
+        <v>4</v>
+      </c>
+      <c r="C4" s="10"/>
       <c r="D4" s="3">
         <v>3</v>
       </c>
@@ -1646,10 +1650,10 @@
       <c r="A5" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="14"/>
+      <c r="B5" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="10"/>
       <c r="D5" s="3">
         <v>4</v>
       </c>
@@ -1662,10 +1666,10 @@
       <c r="A6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="14"/>
+      <c r="B6" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="10"/>
       <c r="D6" s="3">
         <v>5</v>
       </c>
@@ -1710,16 +1714,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:5">
